--- a/output/2026-09-06_13_Slovenia_Posavska_Metalworking_Lavorazioni_Metalliche.xlsx
+++ b/output/2026-09-06_13_Slovenia_Posavska_Metalworking_Lavorazioni_Metalliche.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rete di 7 centri tecnico-commerciali tra cui Krško e Boštanj (Sevnica).</t>
+          <t>Rete di 7 centri tecnico-commerciali tra cui Krško e Boštanj (Sevnica). [DUPLICATO — vedi anche: 2026-09-06_03_Slovenia_Koroska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -594,7 +594,6 @@
           <t>Metalworking / Lavorazioni Metalliche - Macchine per taglio/formatura lamiera (Henkwell, Dowin, Steeltailor, Euram, VMT CNC, BB Makina, Cuteral)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>Telefono/email non trovati nelle fonti pubbliche; azienda verificata (Bizi, sito ufficiale).</t>
@@ -602,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -639,7 +638,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -664,7 +663,6 @@
           <t>Metalworking / Lavorazioni Metalliche - Vendita macchine usate per lavorazione metalli, ricambi</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
           <t>Svolge anche commercio rottami metallici/commutatori (attività mista); telefono/email non reperiti.</t>
@@ -672,7 +670,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -704,7 +702,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Email non reperita nelle fonti pubbliche.</t>
+          <t>Email non reperita nelle fonti pubbliche. [DUPLICATO — vedi anche: 2026-09-06_00_Slovenia_Podravska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -741,7 +739,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Verificata tramite sito ufficiale e directory (Bizi, Info-Slovenija).</t>
+          <t>Verificata tramite sito ufficiale e directory (Bizi, Info-Slovenija). [DUPLICATO — vedi anche: 2026-09-06_00_Slovenia_Podravska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -778,7 +776,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Email reperita da fonte esterna (ifix.si), non presente nella lista originale.</t>
+          <t>Email reperita da fonte esterna (ifix.si), non presente nella lista originale. [DUPLICATO — vedi anche: 2026-09-06_00_Slovenia_Podravska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -820,7 +818,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -852,7 +850,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Confermato anche da profilo LinkedIn (post su Korloy Europa).</t>
+          <t>Confermato anche da profilo LinkedIn (post su Korloy Europa). [DUPLICATO — vedi anche: 2026-09-06_06_Slovenia_Savinjska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -894,7 +892,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -931,7 +929,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (07/09/2026)</t>
         </is>
       </c>
     </row>
@@ -963,7 +961,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Confermato distributore generale Fronius Slovenia con servizio post-vendita.</t>
+          <t>Confermato distributore generale Fronius Slovenia con servizio post-vendita. [DUPLICATO — vedi anche: 2026-09-06_10_Slovenia_Zasavska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
